--- a/addresses.xlsx
+++ b/addresses.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Addresses" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Addresses'!$A$1:$C$51</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -39,7 +41,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002C3E50"/>
+        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +59,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,9 +430,9 @@
   <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1299,6 +1303,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>